--- a/data/trans_orig/IP07KS_C02_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C02_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse lleno/a de energía en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse lleno/a de energía, percibida por el/la menor [KIDSCREEN 10] en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>56,88%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>634</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -838,69 +838,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>657</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37304</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>26501</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44728</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>68,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,72%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>82,23%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>50899</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38959</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59538</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>82,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>27696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27182</t>
+          <t>22224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46802</t>
+          <t>32736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>52599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105637</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9628</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16519</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7213</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1149</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>15814</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>35,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8263</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21492</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27797</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -1741,82 +1741,82 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>999</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1080</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5691</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>999</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1854,47 +1854,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5096</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3644</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>750</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14957</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11253</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18343</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>67,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9962</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6482</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13743</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>47,74%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>24765</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20585</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31185</t>
+          <t>29643</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1894</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>8772</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>12317</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>42,04%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,02%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13761</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>18083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1545</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4341</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,8%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>1677</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>14,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22088</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>22088</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22088</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45051</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12900</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>74,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>28,53%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2515</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>14004</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21778</t>
+          <t>19657</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2879,47 +2879,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>11204</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>64,28%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2357</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>88,96%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>363</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2516</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>11699</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11727</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10809</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7345</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14146</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>53,29%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>6765</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4164</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>9562</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>28,33%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>65,06%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14158</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>22034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -3674,82 +3674,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>1158</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>3762</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>9985</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6145</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>13923</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>51,34%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>7334</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>10637</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>39,8%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>57,73%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>23568</t>
+          <t>22798</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>7584</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>11331</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>38,99%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>58,26%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>9509</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>6471</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>12813</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>51,61%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>69,54%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22574</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,34%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>569</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,27 +4436,27 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>19451</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>18425</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>19363</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39365</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>29290</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>20671</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>35338</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>61,59%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>43,47%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>74,3%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>14236</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>9602</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>18434</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>52,16%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>35,18%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>28785</t>
+          <t>14962</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>19642</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>43020</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33117</t>
+          <t>34374</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>50649</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>13749</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>6909</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22338</t>
+          <t>16320</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>24561</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17735</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>36040</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>5375</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>2247</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>5840</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>21,4%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>743</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4267</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -5264,82 +5264,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>1788</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5397</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>11,7%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,107 +5494,107 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>50984</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>41223</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>59313</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>67,98%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>44524</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>37836</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>50340</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>49129</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>41463</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>56013</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>69,79%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>58,9%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>100113</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>88779</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>110524</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>56,32%</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
         <is>
           <t>70,11%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>79,27%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>47785</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>39645</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>55793</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>48,76%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>68,61%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>92309</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>81932</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>102895</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>63,74%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>56,58%</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>33490</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>25162</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>43223</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>28,84%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>18066</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>24787</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>28,45%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>19,29%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>39,03%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>31002</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>23129</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>38359</t>
+          <t>43367</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>59485</t>
+          <t>64521</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5833,82 +5833,82 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>876</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>876</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>163711</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>146448</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>181516</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>60,83%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>54,42%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>67,45%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>136574</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>119750</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>165248</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>56,9%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>78,51%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>166372</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>148053</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>185299</t>
+          <t>131838</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>302946</t>
+          <t>283091</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>281090</t>
+          <t>261038</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>336945</t>
+          <t>302017</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>84654</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>68859</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>101604</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>31,46%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>37,76%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>62081</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>37962</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>76506</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>82684</t>
+          <t>64968</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>53831</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>149622</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>130502</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>166090</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14606</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>7833</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>28714</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>5591</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>17239</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>15639</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>37399</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>26023</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>16754</t>
+          <t>17546</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>8211</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>982</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -6628,107 +6628,107 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>4456</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>1736</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>269110</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>210472</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>270912</t>
+          <t>197588</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>481384</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
